--- a/data/dados_cerveja_nota.xlsx
+++ b/data/dados_cerveja_nota.xlsx
@@ -11,49 +11,22 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
-    <t>Arredondada</t>
+    <t>id</t>
   </si>
   <si>
-    <t>Suculenta</t>
+    <t>cerveja</t>
   </si>
   <si>
-    <t>Vermelha</t>
-  </si>
-  <si>
-    <t>Doce</t>
-  </si>
-  <si>
-    <t>Fruta</t>
-  </si>
-  <si>
-    <t>Morango</t>
-  </si>
-  <si>
-    <t>Limão</t>
-  </si>
-  <si>
-    <t>Pera</t>
-  </si>
-  <si>
-    <t>Banana</t>
-  </si>
-  <si>
-    <t>Cereja</t>
-  </si>
-  <si>
-    <t>Tomate</t>
-  </si>
-  <si>
-    <t>Maçã</t>
+    <t>nota</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -61,15 +34,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11.0"/>
-      <color rgb="FF5E5E5E"/>
+      <color theme="1"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <color rgb="FF5E5E5E"/>
-      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -86,15 +53,12 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -323,130 +287,170 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="B2" s="2">
+      <c r="A2" s="1">
         <v>1.0</v>
       </c>
-      <c r="C2" s="2">
+      <c r="B2" s="1">
         <v>1.0</v>
       </c>
-      <c r="D2" s="2">
+      <c r="C2" s="1">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="B3" s="1">
         <v>1.0</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="B3" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="C3" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>6</v>
+      <c r="C3" s="1">
+        <v>3.0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="B4" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="C4" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="D4" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>7</v>
+      <c r="A4" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="B4" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1.75</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="B5" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="C5" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="D5" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>8</v>
+      <c r="A5" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="B5" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1.75</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="B6" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="C6" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D6" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>9</v>
+      <c r="A6" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="B6" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C6" s="1">
+        <v>4.2</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="B7" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="C7" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>10</v>
+      <c r="A7" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="B7" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C7" s="1">
+        <v>6.5</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="B8" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="C8" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D8" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>11</v>
+      <c r="A8" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="B8" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="B9" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C9" s="1">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="B10" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C10" s="1">
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="B11" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C11" s="1">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="B12" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C12" s="1">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="B13" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C13" s="1">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="B14" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C14" s="1">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="B15" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C15" s="1">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="B16" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C16" s="1">
+        <v>10.0</v>
       </c>
     </row>
   </sheetData>
